--- a/partner_results/unknown_digitrubber/ClassMissingGermanLabel_unknown_digitrubber.xlsx
+++ b/partner_results/unknown_digitrubber/ClassMissingGermanLabel_unknown_digitrubber.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>instruction step</t>
+          <t>rubber process analyzer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Instruction step is the method of following one instruction at a time in a process to achieve an end objective.</t>
+          <t>A Rubber Process Analyser (RPA) is a scientific instrument used to measure the rheological properties of rubber, particularly its viscoelastic behavior. It applies controlled shear stress and measures the resulting deformation or flow of the rubber.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,7 +469,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>condition specification</t>
+          <t>instruction step</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A condition specification of a process definition refers to the detailed requirements and constraints that must be met within a process to ensure consistency and quality outlining necessary inputs, outputs, parameters that must be controlled to acheive desired outcomes.</t>
+          <t>Instruction step is the method of following one instruction at a time in a process to achieve an end objective.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,12 +492,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ingredient specification</t>
+          <t>mixing recipe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>material specification</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>An ingredient specification is a material specification which is detailed, actionable document defining the quality, safety, and physical characteristics of a raw material</t>
+          <t>A mixing recipe is a recipe which in polymers refers to the specific, controlled formulation and set of operating parameters—including ingredient proportions, sequence of addition, temperature profiles, shear rates, and mixing time—used to combine base polymers with additives, fillers, or other polymers to achieve a uniform, homogeneous mixture with desired physical and chemical properties.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,22 +515,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>measurement metadata</t>
+          <t>ingredient specification</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>material specification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Pallavi Karanth</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>metadata that belong to a measurement. They complete the measurment data providing information about the condition under which the measurements have been taken place.</t>
+          <t>An ingredient specification is a material specification which is detailed, actionable document defining the quality, safety, and physical characteristics of a raw material</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,22 +538,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>device specification set</t>
+          <t>measurement metadata</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Device specifications, often referred to as "tech specs," are detailed descriptions of the technical features and capabilities of a device, including hardware and software components.</t>
+          <t>metadata that belong to a measurement. They complete the measurment data providing information about the condition under which the measurements have been taken place.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,12 +561,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mixing recipe</t>
+          <t>condition specification</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>directive information entity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A mixing recipe is a recipe which in polymers refers to the specific, controlled formulation and set of operating parameters—including ingredient proportions, sequence of addition, temperature profiles, shear rates, and mixing time—used to combine base polymers with additives, fillers, or other polymers to achieve a uniform, homogeneous mixture with desired physical and chemical properties.</t>
+          <t>A condition specification of a process definition refers to the detailed requirements and constraints that must be met within a process to ensure consistency and quality outlining necessary inputs, outputs, parameters that must be controlled to acheive desired outcomes.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -584,37 +584,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deprecated class</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>rubber compound recipe</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lars M Vogt</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>https://orcid.org/0000-0002-8280-0487</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A recipe used in the preparation of a rubber compound.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ingredient specification set</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>material specification</t>
-        </is>
-      </c>
+          <t>deprecated class</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pallavi Karanth</t>
+          <t>Lars M Vogt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ingredient Specification Set is the set of criteria or standards about ingredients to be used in the manufacturing process to attain certain quality or consistency of the end product.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -622,7 +626,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>instruction set</t>
+          <t>objective specification set</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -637,7 +641,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Instruction set is the detailed information about how something should be done or operated.</t>
+          <t>Objective specification set refers to the set of objectives which are the desired characteristics which are to be achieved at the end of a manufacturing process.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -645,22 +649,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rubber compound recipe</t>
+          <t>device specification set</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>directive information entity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-8280-0487</t>
+          <t>Pallavi Karanth</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A recipe used in the preparation of a rubber compound.</t>
+          <t>Device specifications, often referred to as "tech specs," are detailed descriptions of the technical features and capabilities of a device, including hardware and software components.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -668,12 +672,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>objective specification set</t>
+          <t>ingredient specification set</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>material specification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,7 +687,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Objective specification set refers to the set of objectives which are the desired characteristics which are to be achieved at the end of a manufacturing process.</t>
+          <t>Ingredient Specification Set is the set of criteria or standards about ingredients to be used in the manufacturing process to attain certain quality or consistency of the end product.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -691,12 +695,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rubber process analyzer</t>
+          <t>instruction set</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>directive information entity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -706,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A Rubber Process Analyser (RPA) is a scientific instrument used to measure the rheological properties of rubber, particularly its viscoelastic behavior. It applies controlled shear stress and measures the resulting deformation or flow of the rubber.</t>
+          <t>Instruction set is the detailed information about how something should be done or operated.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
